--- a/조사표_원본/시흥캠퍼스_식당카페_조사표_강권재.xlsx
+++ b/조사표_원본/시흥캠퍼스_식당카페_조사표_강권재.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="대분류목록">카테고리!$D$2:$D$3</definedName>
-    <definedName name="식당">카테고리!$A$2:$A$13</definedName>
+    <definedName name="식당">카테고리!$A$2:$A$14</definedName>
     <definedName name="카페">카테고리!$B$2:$B$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'매장·메뉴 입력'!$A$1:$N$401</definedName>
   </definedNames>
@@ -11934,7 +11934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="2"/>
@@ -12063,6 +12063,18 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="141" t="inlineStr">
+        <is>
+          <t>도시락</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12074,7 +12086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -13147,7 +13159,6 @@
         </is>
       </c>
     </row>
-    <row r="22"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13173,7 +13184,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="95" t="inlineStr">
         <is>
@@ -13230,7 +13240,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="95" t="inlineStr">
         <is>
@@ -13371,7 +13380,6 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="95" t="inlineStr">
         <is>
